--- a/tiflow-xborder/build/0.9.0/StructureDefinition-logical-eu-dispense-data.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-logical-eu-dispense-data.xlsx
@@ -332,9 +332,6 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>logical-eu-dispense-data.PatientData</t>
   </si>
   <si>
@@ -375,6 +372,9 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>logical-eu-dispense-data.PatientData.RegionalNationalHealthIdentifier</t>
@@ -1704,7 +1704,7 @@
         <v>80</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>102</v>
@@ -1722,15 +1722,15 @@
         <v>78</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1753,13 +1753,13 @@
         <v>78</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1810,7 +1810,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>87</v>
@@ -1825,7 +1825,7 @@
         <v>84</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>78</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1957,10 +1957,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2074,14 +2074,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2094,25 +2094,25 @@
         <v>78</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N8" t="s" s="2">
         <v>97</v>
       </c>
       <c r="O8" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>78</v>
@@ -2161,7 +2161,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2170,7 +2170,7 @@
         <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>102</v>
@@ -2188,7 +2188,7 @@
         <v>78</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
@@ -2336,7 +2336,7 @@
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>124</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2679,25 +2679,25 @@
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K13" t="s" s="2">
         <v>94</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N13" t="s" s="2">
         <v>97</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>78</v>
@@ -2746,7 +2746,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2755,7 +2755,7 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>102</v>
@@ -2773,7 +2773,7 @@
         <v>78</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -3153,7 +3153,7 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>145</v>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3494,25 +3494,25 @@
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>94</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>97</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3561,7 +3561,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3570,7 +3570,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>102</v>
@@ -3588,7 +3588,7 @@
         <v>78</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
@@ -4555,7 +4555,7 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>190</v>
@@ -4627,10 +4627,10 @@
         <v>84</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4896,25 +4896,25 @@
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>94</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>97</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -4963,7 +4963,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4972,7 +4972,7 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>102</v>
@@ -4990,7 +4990,7 @@
         <v>78</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33">
@@ -5021,7 +5021,7 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>195</v>
@@ -5093,7 +5093,7 @@
         <v>84</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5362,25 +5362,25 @@
         <v>78</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>94</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>97</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5429,7 +5429,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5438,7 +5438,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>102</v>
@@ -5456,7 +5456,7 @@
         <v>78</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
@@ -6187,7 +6187,7 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>230</v>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6528,25 +6528,25 @@
         <v>78</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>94</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>97</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -6595,7 +6595,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6604,7 +6604,7 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>102</v>
@@ -6622,7 +6622,7 @@
         <v>78</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47">
